--- a/zy72506/output/校验明细.xlsx
+++ b/zy72506/output/校验明细.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="160">
   <si>
     <t>样本编号</t>
   </si>
@@ -148,43 +148,25 @@
     <t>模型版本变更但样本编号不变</t>
   </si>
   <si>
-    <t>已导入</t>
-  </si>
-  <si>
-    <t>模型版本冲突</t>
+    <t>待AI产品经理复核</t>
+  </si>
+  <si>
+    <t>AI产品经理已复核</t>
   </si>
   <si>
     <t>已完成</t>
   </si>
   <si>
-    <t>第一步：模型输出导入</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S010 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S009 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S008 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S007 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S006 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S005 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S004 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S003 未变，等待AI产品经理确认</t>
-  </si>
-  <si>
-    <t>模型版本从 v1 变更为 v2，但样本编号 S002 未变，等待AI产品经理确认</t>
+    <t>第二步：AI产品经理补看人工改判表</t>
+  </si>
+  <si>
+    <t>第三步：产品复盘页更新</t>
+  </si>
+  <si>
+    <t>已导入人工改判表，等待AI产品经理阿宁复核</t>
+  </si>
+  <si>
+    <t>复核已完成，等待产品复盘页更新</t>
   </si>
   <si>
     <t>全部流程已完成</t>
@@ -304,7 +286,7 @@
     <t>人工修正后的摘要6</t>
   </si>
   <si>
-    <t>人工修正后的摘要3</t>
+    <t>人工修正S003摘要</t>
   </si>
   <si>
     <t>样本15事实不符</t>
@@ -319,163 +301,199 @@
     <t>样本6事实不符</t>
   </si>
   <si>
-    <t>样本3事实不符</t>
+    <t>样本3事实不符(重新导入)</t>
   </si>
   <si>
     <t>张三</t>
   </si>
   <si>
-    <t>确认版本变更有效，模型输出已更新</t>
+    <t>S008:驳回，无需运营复核</t>
+  </si>
+  <si>
+    <t>S007:v2版本正确</t>
+  </si>
+  <si>
+    <t>S006:补充证据后再次确认</t>
+  </si>
+  <si>
+    <t>v2版本输出更准确，重新确认有效</t>
   </si>
   <si>
     <t>阿宁</t>
   </si>
   <si>
-    <t>2026-06-07T11:46:40.742774</t>
-  </si>
-  <si>
-    <t>确认通过，版本变更有效</t>
-  </si>
-  <si>
-    <t>运营李四</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:46:47.351258</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.780436</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.779201</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.777447</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.773426</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.769825</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.767823</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.766359</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.763395</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.761042</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.757885</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.755961</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.753694</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.752027</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.750098</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.744154</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.780442</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.779205</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.777457</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.773451</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.769830</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.767827</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.766364</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.763402</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.761071</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.757890</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.755968</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.753698</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.752035</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:45:45.750107</t>
-  </si>
-  <si>
-    <t>2026-06-07T11:47:00.257988</t>
-  </si>
-  <si>
-    <t>470a6bbb-ddfd-49d3-9299-87da89f8faf4</t>
-  </si>
-  <si>
-    <t>cc602f22-f3cf-4c73-a7a3-23561194f937</t>
-  </si>
-  <si>
-    <t>ed288515-92c3-4917-b33e-1c85eae11002</t>
-  </si>
-  <si>
-    <t>51ccec20-7d2f-4b92-bb2b-0a57745a0491</t>
-  </si>
-  <si>
-    <t>cb5d5d76-a3d7-4337-b52a-e20b8297b97a</t>
-  </si>
-  <si>
-    <t>c0c20403-794b-4680-a2f6-533413aac35c</t>
-  </si>
-  <si>
-    <t>1e2202b0-a4cd-41b8-b3ca-71c8fe5572bc</t>
-  </si>
-  <si>
-    <t>fa7c69df-cf9c-4ff7-83ad-335ded78a489</t>
-  </si>
-  <si>
-    <t>7baa2b14-f8fa-4619-85fb-b93bd1836996</t>
-  </si>
-  <si>
-    <t>bd7c62d6-ac21-42bf-8fce-719c08a98232</t>
-  </si>
-  <si>
-    <t>ba147220-2f82-4068-8996-b8afb3bf1f8d</t>
-  </si>
-  <si>
-    <t>af81d638-fb52-4fb0-ac79-c3fe7b924b4f</t>
-  </si>
-  <si>
-    <t>159ec349-d31b-4343-80db-02a05820be11</t>
-  </si>
-  <si>
-    <t>8ab6d8ec-2426-46fd-9ed7-0a0b89a772c9</t>
-  </si>
-  <si>
-    <t>5ab68410-5a81-4376-8551-ff016134aa57</t>
+    <t>2026-06-20T10:27:29.214670</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:27:20.871035</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:26:57.477917</t>
+  </si>
+  <si>
+    <t>2026-06-13T11:19:00.316444</t>
+  </si>
+  <si>
+    <t>S007:事实准确</t>
+  </si>
+  <si>
+    <t>S006:最终通过</t>
+  </si>
+  <si>
+    <t>与原始证据核对无误，重新确认</t>
+  </si>
+  <si>
+    <t>运营李哥</t>
+  </si>
+  <si>
+    <t>运营张姐</t>
+  </si>
+  <si>
+    <t>运营王小明</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:27:20.872436</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:27:11.358403</t>
+  </si>
+  <si>
+    <t>2026-06-13T11:19:00.317357</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.887473</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.886714</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.885878</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.885121</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.884272</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.883532</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.882585</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.881670</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.880718</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.879492</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.878077</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.877148</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.876025</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.874935</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:43.873824</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.597591</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.596420</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.595242</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.594321</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.593341</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.592372</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.591287</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:27:29.214685</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:27:20.873738</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:27:11.368977</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.587413</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.586211</t>
+  </si>
+  <si>
+    <t>2026-06-13T11:19:00.318496</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.583768</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:50:51.582477</t>
+  </si>
+  <si>
+    <t>5d29f378-6be8-4fff-841e-23a093b07c63</t>
+  </si>
+  <si>
+    <t>8f0eb3e0-1f08-48f1-8507-0162d6d7f0e6</t>
+  </si>
+  <si>
+    <t>1662f3c0-e761-4ad7-b0cf-6f1b06108d8a</t>
+  </si>
+  <si>
+    <t>f476b986-5c91-4825-8d07-caa679f3a2c8</t>
+  </si>
+  <si>
+    <t>f28116f5-ee65-48dc-84e1-43c632ac618c</t>
+  </si>
+  <si>
+    <t>fd272a9c-cd12-4fe0-8779-0a33801f2d9d</t>
+  </si>
+  <si>
+    <t>d97d4e82-6bda-47bc-bd42-685566f50bff</t>
+  </si>
+  <si>
+    <t>2e95edd9-f595-484f-8e1a-aeabba70d68d</t>
+  </si>
+  <si>
+    <t>ec551f09-90b0-42d7-bf1f-f5f7bb68509d</t>
+  </si>
+  <si>
+    <t>decd6481-f16a-4528-9f84-a5daeb02cf46</t>
+  </si>
+  <si>
+    <t>e6fd154a-4c0b-4ab1-b959-d324d441cbfa</t>
+  </si>
+  <si>
+    <t>6f2d8561-0fba-4832-b6d3-19799ec2ca1b</t>
+  </si>
+  <si>
+    <t>cbc35560-3f1d-452a-ad3f-f742e327a3d1</t>
+  </si>
+  <si>
+    <t>e78f5c6a-d44f-4678-a087-a15e54a148b9</t>
+  </si>
+  <si>
+    <t>10ccfc40-b645-479e-90ca-1f2982ba849a</t>
   </si>
 </sst>
 </file>
@@ -929,38 +947,44 @@
       <c r="F2" t="s">
         <v>44</v>
       </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
+        <v>49</v>
+      </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L2">
         <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="O2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="P2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="X2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="Y2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -979,32 +1003,38 @@
       <c r="F3" t="s">
         <v>44</v>
       </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>49</v>
+      </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L3">
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="X3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="Y3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1023,32 +1053,38 @@
       <c r="F4" t="s">
         <v>44</v>
       </c>
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
       <c r="I4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L4">
         <v>14</v>
       </c>
       <c r="M4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="X4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="Y4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1067,38 +1103,44 @@
       <c r="F5" t="s">
         <v>44</v>
       </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
+      </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="J5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L5">
         <v>13</v>
       </c>
       <c r="M5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="X5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="Y5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1117,32 +1159,38 @@
       <c r="F6" t="s">
         <v>44</v>
       </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L6">
         <v>12</v>
       </c>
       <c r="M6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="X6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="Y6" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1162,40 +1210,40 @@
         <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
         <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L7">
         <v>11</v>
       </c>
       <c r="M7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="X7" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="Y7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1215,7 +1263,7 @@
         <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
         <v>47</v>
@@ -1224,37 +1272,37 @@
         <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L8">
         <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N8" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="O8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="P8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W8" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="X8" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="Y8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1277,37 +1325,46 @@
         <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H9" t="s">
         <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L9">
         <v>9</v>
       </c>
       <c r="M9" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P9" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>97</v>
+      </c>
+      <c r="R9" t="s">
+        <v>101</v>
+      </c>
+      <c r="S9" t="s">
         <v>102</v>
       </c>
       <c r="W9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="X9" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="Y9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1327,40 +1384,55 @@
         <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>51</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L10">
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>102</v>
+        <v>96</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>98</v>
+      </c>
+      <c r="R10" t="s">
+        <v>101</v>
+      </c>
+      <c r="S10" t="s">
+        <v>103</v>
+      </c>
+      <c r="T10" t="s">
+        <v>106</v>
+      </c>
+      <c r="U10" t="s">
+        <v>109</v>
+      </c>
+      <c r="V10" t="s">
+        <v>112</v>
       </c>
       <c r="W10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="X10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="Y10" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1380,46 +1452,61 @@
         <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J11" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" t="s">
         <v>82</v>
-      </c>
-      <c r="K11" t="s">
-        <v>88</v>
       </c>
       <c r="L11">
         <v>7</v>
       </c>
       <c r="M11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="N11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>102</v>
+        <v>96</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>99</v>
+      </c>
+      <c r="R11" t="s">
+        <v>101</v>
+      </c>
+      <c r="S11" t="s">
+        <v>104</v>
+      </c>
+      <c r="T11" t="s">
+        <v>107</v>
+      </c>
+      <c r="U11" t="s">
+        <v>110</v>
+      </c>
+      <c r="V11" t="s">
+        <v>113</v>
       </c>
       <c r="W11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="X11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="Y11" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1439,40 +1526,40 @@
         <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12" t="s">
         <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L12">
         <v>6</v>
       </c>
       <c r="M12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="X12" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="Y12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1492,40 +1579,40 @@
         <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
         <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L13">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W13" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="X13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="Y13" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1545,46 +1632,61 @@
         <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I14" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L14">
         <v>4</v>
       </c>
       <c r="M14" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" t="s">
         <v>90</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
+        <v>95</v>
+      </c>
+      <c r="P14" t="s">
         <v>96</v>
       </c>
-      <c r="O14" t="s">
+      <c r="Q14" t="s">
+        <v>100</v>
+      </c>
+      <c r="R14" t="s">
         <v>101</v>
       </c>
-      <c r="P14" t="s">
-        <v>102</v>
+      <c r="S14" t="s">
+        <v>105</v>
+      </c>
+      <c r="T14" t="s">
+        <v>108</v>
+      </c>
+      <c r="U14" t="s">
+        <v>111</v>
+      </c>
+      <c r="V14" t="s">
+        <v>114</v>
       </c>
       <c r="W14" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="X14" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="Y14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1604,40 +1706,40 @@
         <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
         <v>47</v>
       </c>
       <c r="H15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I15" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L15">
         <v>3</v>
       </c>
       <c r="M15" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="W15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="X15" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Y15" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1657,55 +1759,40 @@
         <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J16" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L16">
         <v>2</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>103</v>
-      </c>
-      <c r="R16" t="s">
-        <v>104</v>
-      </c>
-      <c r="S16" t="s">
-        <v>105</v>
-      </c>
-      <c r="T16" t="s">
-        <v>106</v>
-      </c>
-      <c r="U16" t="s">
-        <v>107</v>
-      </c>
-      <c r="V16" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="W16" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="X16" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="Y16" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
